--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaibhav dwivedi\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59017C8D-76EA-496D-86D1-91E78154D370}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2380,26 +2380,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B34" s="14">
+        <v>600</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>150</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>20</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59017C8D-76EA-496D-86D1-91E78154D370}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E28848-4FE7-40EA-B3FE-47B2E6383BFE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>feeling happy today because no class today.</t>
+  </si>
+  <si>
+    <t>felling happy.</t>
   </si>
 </sst>
 </file>
@@ -595,6 +598,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2426,48 +2433,96 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>50</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>30</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E28848-4FE7-40EA-B3FE-47B2E6383BFE}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBB3DA99-3F45-4ED0-ABF7-E9BF54082DAE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,12 @@
   </si>
   <si>
     <t>felling happy.</t>
+  </si>
+  <si>
+    <t>Good.</t>
+  </si>
+  <si>
+    <t>felling stressed.</t>
   </si>
 </sst>
 </file>
@@ -2525,48 +2531,96 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>20</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>400</v>
+      </c>
+      <c r="G37" s="14">
+        <v>8</v>
+      </c>
+      <c r="H37" s="14">
+        <v>30</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>50</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>90</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>0</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBB3DA99-3F45-4ED0-ABF7-E9BF54082DAE}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{336C72F3-9148-49E0-965B-5D8F5F922A09}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2623,26 +2623,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>240</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>6</v>
+      </c>
+      <c r="H39" s="14">
+        <v>20</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{336C72F3-9148-49E0-965B-5D8F5F922A09}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A3EE3D6-B6FC-47B3-9BAB-05DB1D34B6C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>felling stressed.</t>
+  </si>
+  <si>
+    <t>felling happy because today's CA is held very good.</t>
   </si>
 </sst>
 </file>
@@ -2668,49 +2671,97 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>180</v>
+      </c>
+      <c r="E40" s="14">
+        <v>90</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>30</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B41" s="14">
+        <v>480</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>90</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A3EE3D6-B6FC-47B3-9BAB-05DB1D34B6C9}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C72066B-F423-42DE-B8FA-390721C807FA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2764,48 +2764,96 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>60</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>90</v>
+      </c>
+      <c r="F42" s="14">
+        <v>100</v>
+      </c>
+      <c r="G42" s="14">
+        <v>2</v>
+      </c>
+      <c r="H42" s="14">
+        <v>90</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>60</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>90</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C72066B-F423-42DE-B8FA-390721C807FA}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6C10A7-7093-4A33-BF29-4AD547337414}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -138,7 +138,7 @@
     <t>Name:</t>
   </si>
   <si>
-    <t>Vaibhav Dwivedi</t>
+    <t>Sonu kumar</t>
   </si>
   <si>
     <t>Registration No.:</t>
@@ -313,6 +313,18 @@
   </si>
   <si>
     <t>felling happy because today's CA is held very good.</t>
+  </si>
+  <si>
+    <t>medium.</t>
+  </si>
+  <si>
+    <t>happy.</t>
+  </si>
+  <si>
+    <t>terrorist like activity in the campus.</t>
+  </si>
+  <si>
+    <t>again terrorist like activity and huge chaos inside campus.</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1038,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="21">
-        <v>12600738</v>
+        <v>12629810</v>
       </c>
       <c r="G2" s="21"/>
     </row>
@@ -2811,7 +2823,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B43" s="14">
         <v>480</v>
@@ -2856,124 +2868,260 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>400</v>
+      </c>
+      <c r="G44" s="14">
+        <v>8</v>
+      </c>
+      <c r="H44" s="14">
+        <v>0</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B45" s="14">
+        <v>360</v>
+      </c>
+      <c r="C45" s="14">
+        <v>20</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>90</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>20</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>90</v>
+      </c>
+      <c r="E46" s="14">
+        <v>120</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6</v>
+      </c>
+      <c r="H46" s="14">
+        <v>30</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B47" s="14">
+        <v>480</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>90</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>30</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B48" s="14">
+        <v>0</v>
+      </c>
+      <c r="C48" s="14">
+        <v>50</v>
+      </c>
+      <c r="D48" s="14">
+        <v>90</v>
+      </c>
+      <c r="E48" s="14">
+        <v>60</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>0</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>200</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
+        <v>1240</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B49" s="14">
+        <v>0</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>0</v>
+      </c>
       <c r="I49" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2982,10 +3130,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+      <c r="K49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6C10A7-7093-4A33-BF29-4AD547337414}"/>
+  <xr:revisionPtr revIDLastSave="377" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8A5BECC-B941-403F-8A01-6BCCC3E91112}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>Name:</t>
-  </si>
-  <si>
-    <t>Sonu kumar</t>
   </si>
   <si>
     <t>Registration No.:</t>
@@ -325,6 +322,12 @@
   </si>
   <si>
     <t>again terrorist like activity and huge chaos inside campus.</t>
+  </si>
+  <si>
+    <t>VAIBHAV DWIVEDI</t>
+  </si>
+  <si>
+    <t>very happy.</t>
   </si>
 </sst>
 </file>
@@ -619,10 +622,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1030,38 +1029,38 @@
         <v>31</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="21">
-        <v>12629810</v>
+        <v>12600738</v>
       </c>
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>34</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>37</v>
       </c>
       <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1079,46 +1078,46 @@
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1155,16 +1154,16 @@
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1193,24 +1192,24 @@
         <v>20</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>880</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I7="","",1440-I7)</f>
         <v>560</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>54</v>
-      </c>
       <c r="M7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1239,24 +1238,24 @@
         <v>60</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v>950</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I8="","",1440-I8)</f>
         <v>490</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="M8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>61</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1293,16 +1292,16 @@
         <v>360</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1339,16 +1338,16 @@
         <v>410</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1385,16 +1384,16 @@
         <v>570</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N11" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1431,16 +1430,16 @@
         <v>570</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>54</v>
-      </c>
       <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>57</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1477,16 +1476,16 @@
         <v>540</v>
       </c>
       <c r="K13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1523,16 +1522,16 @@
         <v>450</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N14" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1569,16 +1568,16 @@
         <v>390</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1615,16 +1614,16 @@
         <v>440</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1661,16 +1660,16 @@
         <v>450</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1707,16 +1706,16 @@
         <v>430</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1753,16 +1752,16 @@
         <v>640</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1799,16 +1798,16 @@
         <v>670</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="16" t="s">
-        <v>54</v>
-      </c>
       <c r="M20" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1845,16 +1844,16 @@
         <v>620</v>
       </c>
       <c r="K21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M21" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N21" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1891,16 +1890,16 @@
         <v>460</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
         <v>78</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1937,16 +1936,16 @@
         <v>380</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N23" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1983,16 +1982,16 @@
         <v>510</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2029,14 +2028,14 @@
         <v>460</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M25" s="16"/>
       <c r="N25" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2073,16 +2072,16 @@
         <v>710</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L26" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2119,16 +2118,16 @@
         <v>640</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L27" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N27" s="17" t="s">
         <v>83</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2165,16 +2164,16 @@
         <v>640</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2211,16 +2210,16 @@
         <v>400</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M29" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N29" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2257,16 +2256,16 @@
         <v>320</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2303,16 +2302,16 @@
         <v>510</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2349,16 +2348,16 @@
         <v>390</v>
       </c>
       <c r="K32" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L32" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L32" s="16" t="s">
+      <c r="M32" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M32" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N32" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2395,16 +2394,16 @@
         <v>610</v>
       </c>
       <c r="K33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L33" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="L33" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="M33" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2441,16 +2440,16 @@
         <v>530</v>
       </c>
       <c r="K34" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L34" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L34" s="16" t="s">
+      <c r="M34" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M34" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N34" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2487,16 +2486,16 @@
         <v>600</v>
       </c>
       <c r="K35" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L35" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L35" s="16" t="s">
+      <c r="M35" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M35" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N35" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2533,16 +2532,16 @@
         <v>490</v>
       </c>
       <c r="K36" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L36" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="L36" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="M36" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2579,16 +2578,16 @@
         <v>330</v>
       </c>
       <c r="K37" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="16" t="s">
+      <c r="M37" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M37" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N37" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2625,16 +2624,16 @@
         <v>450</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2671,16 +2670,16 @@
         <v>370</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2717,16 +2716,16 @@
         <v>750</v>
       </c>
       <c r="K40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="L40" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="M40" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2763,16 +2762,16 @@
         <v>630</v>
       </c>
       <c r="K41" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L41" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="L41" s="16" t="s">
-        <v>68</v>
-      </c>
       <c r="M41" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2809,16 +2808,16 @@
         <v>560</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2855,16 +2854,16 @@
         <v>270</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2901,16 +2900,16 @@
         <v>410</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2947,16 +2946,16 @@
         <v>580</v>
       </c>
       <c r="K45" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L45" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L45" s="16" t="s">
+      <c r="M45" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M45" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="N45" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -2993,16 +2992,16 @@
         <v>450</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M46" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -3039,16 +3038,16 @@
         <v>470</v>
       </c>
       <c r="K47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L47" s="16" t="s">
+      <c r="M47" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M47" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N47" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3085,16 +3084,16 @@
         <v>1240</v>
       </c>
       <c r="K48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L48" s="16" t="s">
+      <c r="M48" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M48" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N48" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3131,171 +3130,339 @@
         <v/>
       </c>
       <c r="K49" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M49" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>30</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>90</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>120</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B51" s="14">
+        <v>500</v>
+      </c>
+      <c r="C51" s="14">
+        <v>60</v>
+      </c>
+      <c r="D51" s="14">
+        <v>150</v>
+      </c>
+      <c r="E51" s="14">
+        <v>120</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>60</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B52" s="14">
+        <v>520</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>120</v>
+      </c>
+      <c r="E52" s="14">
+        <v>90</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>90</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B53" s="14">
+        <v>520</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>90</v>
+      </c>
+      <c r="E53" s="14">
+        <v>120</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>60</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B54" s="14">
+        <v>420</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>120</v>
+      </c>
+      <c r="E54" s="14">
+        <v>120</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>60</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B55" s="14">
+        <v>540</v>
+      </c>
+      <c r="C55" s="14">
+        <v>60</v>
+      </c>
+      <c r="D55" s="14">
+        <v>120</v>
+      </c>
+      <c r="E55" s="14">
+        <v>90</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>30</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B56" s="14">
+        <v>480</v>
+      </c>
+      <c r="C56" s="14">
+        <v>30</v>
+      </c>
+      <c r="D56" s="14">
+        <v>90</v>
+      </c>
+      <c r="E56" s="14">
+        <v>90</v>
+      </c>
+      <c r="F56" s="14">
+        <v>100</v>
+      </c>
+      <c r="G56" s="14">
+        <v>2</v>
+      </c>
+      <c r="H56" s="14">
+        <v>30</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
@@ -10902,16 +11069,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L25 L28:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L28:L401 L6:L25" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M25 M27:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M27:M401 M6:M25" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8A5BECC-B941-403F-8A01-6BCCC3E91112}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D71E0D6-2820-444B-9A2D-5FCF6B27E72E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3465,114 +3465,234 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>120</v>
+      </c>
+      <c r="E57" s="14">
+        <v>120</v>
+      </c>
+      <c r="F57" s="14">
+        <v>300</v>
+      </c>
+      <c r="G57" s="14">
+        <v>6</v>
+      </c>
+      <c r="H57" s="14">
+        <v>20</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B58" s="14">
+        <v>360</v>
+      </c>
+      <c r="C58" s="14">
+        <v>45</v>
+      </c>
+      <c r="D58" s="14">
+        <v>90</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>400</v>
+      </c>
+      <c r="G58" s="14">
+        <v>8</v>
+      </c>
+      <c r="H58" s="14">
+        <v>50</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B59" s="14">
+        <v>360</v>
+      </c>
+      <c r="C59" s="14">
+        <v>45</v>
+      </c>
+      <c r="D59" s="14">
+        <v>120</v>
+      </c>
+      <c r="E59" s="14">
+        <v>90</v>
+      </c>
+      <c r="F59" s="14">
+        <v>250</v>
+      </c>
+      <c r="G59" s="14">
+        <v>5</v>
+      </c>
+      <c r="H59" s="14">
+        <v>60</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>925</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>515</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>50</v>
+      </c>
+      <c r="D60" s="14">
+        <v>90</v>
+      </c>
+      <c r="E60" s="14">
+        <v>120</v>
+      </c>
+      <c r="F60" s="14">
+        <v>300</v>
+      </c>
+      <c r="G60" s="14">
+        <v>6</v>
+      </c>
+      <c r="H60" s="14">
+        <v>50</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B61" s="14">
+        <v>360</v>
+      </c>
+      <c r="C61" s="14">
+        <v>60</v>
+      </c>
+      <c r="D61" s="14">
+        <v>240</v>
+      </c>
+      <c r="E61" s="14">
+        <v>90</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>30</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D71E0D6-2820-444B-9A2D-5FCF6B27E72E}"/>
+  <xr:revisionPtr revIDLastSave="596" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB4867F6-C9F9-4C44-BBB5-F91BC39D2ECA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,12 @@
   </si>
   <si>
     <t>very happy.</t>
+  </si>
+  <si>
+    <t>mid-term started.</t>
+  </si>
+  <si>
+    <t>mid-term ended.</t>
   </si>
 </sst>
 </file>
@@ -3055,7 +3061,7 @@
         <v>46292</v>
       </c>
       <c r="B48" s="14">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="C48" s="14">
         <v>50</v>
@@ -3073,15 +3079,15 @@
         <v>0</v>
       </c>
       <c r="H48" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>620</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>1240</v>
+        <v>820</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>58</v>
@@ -3101,16 +3107,16 @@
         <v>46293</v>
       </c>
       <c r="B49" s="14">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="C49" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D49" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E49" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F49" s="14">
         <v>0</v>
@@ -3119,15 +3125,15 @@
         <v>0</v>
       </c>
       <c r="H49" s="14">
-        <v>0</v>
-      </c>
-      <c r="I49" s="15" t="str">
+        <v>120</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>600</v>
       </c>
       <c r="K49" s="16" t="s">
         <v>58</v>
@@ -3695,268 +3701,556 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B62" s="14">
+        <v>420</v>
+      </c>
+      <c r="C62" s="14">
+        <v>50</v>
+      </c>
+      <c r="D62" s="14">
+        <v>360</v>
+      </c>
+      <c r="E62" s="14">
+        <v>90</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>20</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B63" s="14">
+        <v>480</v>
+      </c>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>360</v>
+      </c>
+      <c r="E63" s="14">
+        <v>180</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>0</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="14">
+        <v>420</v>
+      </c>
+      <c r="C64" s="14">
+        <v>50</v>
+      </c>
+      <c r="D64" s="14">
+        <v>360</v>
+      </c>
+      <c r="E64" s="14">
+        <v>90</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>20</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B65" s="14">
+        <v>240</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>240</v>
+      </c>
+      <c r="E65" s="14">
+        <v>180</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>30</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B66" s="14">
+        <v>480</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>480</v>
+      </c>
+      <c r="E66" s="14">
+        <v>90</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>20</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B67" s="14">
+        <v>360</v>
+      </c>
+      <c r="C67" s="14">
+        <v>20</v>
+      </c>
+      <c r="D67" s="14">
+        <v>360</v>
+      </c>
+      <c r="E67" s="14">
+        <v>120</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>30</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B68" s="14">
+        <v>300</v>
+      </c>
+      <c r="C68" s="14">
+        <v>30</v>
+      </c>
+      <c r="D68" s="14">
+        <v>360</v>
+      </c>
+      <c r="E68" s="14">
+        <v>120</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>40</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B69" s="14">
+        <v>360</v>
+      </c>
+      <c r="C69" s="14">
+        <v>30</v>
+      </c>
+      <c r="D69" s="14">
+        <v>120</v>
+      </c>
+      <c r="E69" s="14">
+        <v>120</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>40</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>770</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B70" s="14">
+        <v>420</v>
+      </c>
+      <c r="C70" s="14">
+        <v>60</v>
+      </c>
+      <c r="D70" s="14">
+        <v>180</v>
+      </c>
+      <c r="E70" s="14">
+        <v>120</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>30</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B71" s="14">
+        <v>360</v>
+      </c>
+      <c r="C71" s="14">
+        <v>50</v>
+      </c>
+      <c r="D71" s="14">
+        <v>180</v>
+      </c>
+      <c r="E71" s="14">
+        <v>90</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>50</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>60</v>
+      </c>
+      <c r="D72" s="14">
+        <v>120</v>
+      </c>
+      <c r="E72" s="14">
+        <v>120</v>
+      </c>
+      <c r="F72" s="14">
+        <v>400</v>
+      </c>
+      <c r="G72" s="14">
+        <v>8</v>
+      </c>
+      <c r="H72" s="14">
+        <v>20</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B73" s="14">
+        <v>40</v>
+      </c>
+      <c r="C73" s="14">
+        <v>60</v>
+      </c>
+      <c r="D73" s="14">
+        <v>120</v>
+      </c>
+      <c r="E73" s="14">
+        <v>90</v>
+      </c>
+      <c r="F73" s="14">
+        <v>250</v>
+      </c>
+      <c r="G73" s="14">
+        <v>5</v>
+      </c>
+      <c r="H73" s="14">
+        <v>30</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
